--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-Altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-Altersgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T20:13:59+00:00</t>
+    <t>2025-02-20T20:24:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-Altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-Altersgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T20:24:20+00:00</t>
+    <t>2025-02-27T10:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-Altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-Altersgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T10:01:21+00:00</t>
+    <t>2025-02-27T10:07:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-Altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-Altersgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T10:07:48+00:00</t>
+    <t>2025-03-01T14:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-Altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-Altersgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T14:47:03+00:00</t>
+    <t>2025-03-01T14:53:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-Altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-Altersgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T14:53:36+00:00</t>
+    <t>2025-03-01T15:19:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-Altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-Altersgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T15:19:11+00:00</t>
+    <t>2025-03-02T20:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-Altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-Altersgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T20:51:11+00:00</t>
+    <t>2025-03-02T20:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-Altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-Altersgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T20:57:05+00:00</t>
+    <t>2025-03-11T16:13:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-Altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-Altersgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T16:13:30+00:00</t>
+    <t>2025-03-11T16:22:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-Altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-Altersgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T16:22:04+00:00</t>
+    <t>2025-03-12T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-Altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-Altersgruppe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T12:46:26+00:00</t>
+    <t>2025-03-12T14:39:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
